--- a/LeetCode.xlsx
+++ b/LeetCode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/md/Desktop/coding_problems/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C43B74-78CD-004D-A72D-DE7144EEA5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5424C9-8BD8-AE4A-AD4E-1A0F6113081E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26580" yWindow="2740" windowWidth="22480" windowHeight="19560" xr2:uid="{E09DF6F4-896D-2F4D-AC2A-920FC9313AE8}"/>
+    <workbookView xWindow="24160" yWindow="1460" windowWidth="24620" windowHeight="25060" xr2:uid="{E09DF6F4-896D-2F4D-AC2A-920FC9313AE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="170">
   <si>
     <t>Type</t>
   </si>
@@ -540,6 +540,12 @@
   </si>
   <si>
     <t>Contains Duplicate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>边数 = node - 1 先判断</t>
   </si>
 </sst>
 </file>
@@ -549,7 +555,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -594,14 +600,6 @@
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -683,7 +681,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -697,7 +695,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -769,24 +767,12 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -797,6 +783,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1140,7 +1135,7 @@
     <col min="1" max="1" width="10.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="20.1640625" style="3"/>
     <col min="3" max="3" width="37.83203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" style="38"/>
+    <col min="4" max="4" width="20.1640625" style="34"/>
     <col min="5" max="5" width="29.1640625" style="3" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="3" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" style="3" customWidth="1"/>
@@ -2026,27 +2021,27 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="34" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="31">
+    <row r="41" spans="1:8" s="37" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="35">
         <v>5</v>
       </c>
-      <c r="B41" s="31" t="s">
+      <c r="B41" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="32" t="s">
+      <c r="C41" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="36">
         <v>45838</v>
       </c>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31" t="s">
+      <c r="E41" s="35"/>
+      <c r="F41" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="31" t="s">
+      <c r="H41" s="35" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2122,25 +2117,25 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="1">
-        <v>5</v>
-      </c>
-      <c r="B45" s="1" t="s">
+    <row r="45" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="6">
         <v>45886</v>
       </c>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1" t="s">
+      <c r="E45" s="4"/>
+      <c r="F45" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1" t="s">
+      <c r="G45" s="4"/>
+      <c r="H45" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2177,7 +2172,9 @@
       <c r="D47" s="2">
         <v>45894</v>
       </c>
-      <c r="E47" s="1"/>
+      <c r="E47" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1" t="s">
         <v>10</v>
@@ -3127,7 +3124,7 @@
       <c r="B92" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C92" s="35" t="s">
+      <c r="C92" s="31" t="s">
         <v>94</v>
       </c>
       <c r="D92" s="2">
@@ -3179,7 +3176,7 @@
       <c r="B94" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C94" s="35" t="s">
+      <c r="C94" s="31" t="s">
         <v>93</v>
       </c>
       <c r="D94" s="2">
@@ -3481,16 +3478,16 @@
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108" s="36">
+      <c r="A108" s="32">
         <v>13.5</v>
       </c>
-      <c r="B108" s="36"/>
-      <c r="C108" s="36"/>
-      <c r="D108" s="37"/>
-      <c r="E108" s="36"/>
-      <c r="F108" s="36"/>
-      <c r="G108" s="36"/>
-      <c r="H108" s="36"/>
+      <c r="B108" s="32"/>
+      <c r="C108" s="32"/>
+      <c r="D108" s="33"/>
+      <c r="E108" s="32"/>
+      <c r="F108" s="32"/>
+      <c r="G108" s="32"/>
+      <c r="H108" s="32"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H111">
